--- a/internal_doc/05.测试设计/OM/数据操作/OM-数据操作（主界面）-测试用例.xlsx
+++ b/internal_doc/05.测试设计/OM/数据操作/OM-数据操作（主界面）-测试用例.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="31">
   <si>
     <t>name</t>
   </si>
@@ -49,135 +49,113 @@
   </si>
   <si>
     <t>execution_type2</t>
-  </si>
-  <si>
-    <t>前置条件</t>
-  </si>
-  <si>
-    <t>执行步骤</t>
-  </si>
-  <si>
-    <t>期望结果</t>
-  </si>
-  <si>
-    <t>步骤执行方式（手动写1）</t>
-  </si>
-  <si>
-    <t>步骤序号（1、2、3、……）</t>
-  </si>
-  <si>
-    <t>建议为测试用例标题</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>用例执行方式（手动写1自动写2）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>重要性（1高2中3低）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>测试用例摘要（测试目的）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>列表数据正确性检查</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>链接测试</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>分页功能测试</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>后台新增集合后页面点击‘刷新’图标刷新列表数据</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>列表字段排序</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>列表数据展示方式检查（字符串、视图、列表方式）</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>1、进入“数据操作”页面
 2、检查集群下集合数据正确性，包括集合所属集合空间、分区类型、记录数、Lob数等</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>集群下集合数据展示正确</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>1、进入“数据操作”页面
 2、检查该集群下列表中各链接跳转页面正确，且页面数据展示正确，包括集合、记录数、Lob数等</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>1、点击“集合”链接，跳转到该集合列表页面，页面跳转正确，且数据正确；
 2、点击“记录数”链接，跳转到该集合列表页面，页面跳转正确，且数据正确；
 3、点击“Lob数”链接，跳转到该集合列表页面，页面跳转正确，且数据正确；</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>1、进入“数据操作”页面
 2、列表下方输入要跳转至的页数，覆盖：
    0、-1、小于当前总页数、等于当前总页数、大于当前总页数</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>1、输入页数小于当前总页数，跳转至输入的页
 2、输入的页数为0、-1、小于当前总页数、等于当前总页数、大于当前总页数，跳转至首页</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>1、进入“数据操作”页面
 2、检查列表集合名和集合总个数
 3、登录后台sdb shell，创建集合A
 4、OM页面点击列表下方“刷新”按钮，查看后台新创建的集合A是否在页面正常展示</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>刷新成功，新增集合被刷新到当前列表，且数据展示正确</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>1、进入“数据操作”页面
 2、点击列表列名排序，包括所有列
 3、检查按列名排序正确性</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>列表数据按指定列名排序成功，数据按排序方式正确展示</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>1、进入“数据操作”页面
 2、点击“记录数”进入到记录列表页面，点击列表下方的‘字符串’、‘视图’、‘列表方式’，检查数据展示正确性</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>记录按不同的展示方式展示的数据正确</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>1、数据库环境运行正常
 2、已创建集合空间、集合
 3、登录OM首页，选择集群下的“业务”，进入“业务列表”界面，选择对应业务名进入“数据”页面</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>列表数据正确性检查_om.mainPage.001</t>
+  </si>
+  <si>
+    <t>链接测试_om.mainPage.002</t>
+  </si>
+  <si>
+    <t>分页功能测试_om.mainPage.003</t>
+  </si>
+  <si>
+    <t>列表字段排序_om.mainPage.005</t>
+  </si>
+  <si>
+    <t>后台新增集合后页面点击‘刷新’_om.mainPage.004</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>按钮测试_om.mainPage.006</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入信息中心--&gt;安装--&gt;安装部署--&gt;可视化数据操作--&gt;数据库操作
+2、检查资料描述正确性</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>资料描述正确，描述内容与实际操作一致，可正确指导用户操作</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>资料测试_om.mainPage.007</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -185,12 +163,6 @@
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
@@ -213,7 +185,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -221,11 +193,22 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -233,14 +216,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -637,7 +621,7 @@
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="26.375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="30" style="5" customWidth="1"/>
+    <col min="2" max="2" width="30" style="4" customWidth="1"/>
     <col min="3" max="3" width="33.625" style="1" customWidth="1"/>
     <col min="4" max="6" width="5" style="1" customWidth="1"/>
     <col min="7" max="7" width="44.375" style="1" customWidth="1"/>
@@ -675,193 +659,189 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="36.75" customHeight="1">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:9" ht="67.5">
+      <c r="A2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" s="3">
+        <v>2</v>
+      </c>
+      <c r="E2" s="3">
+        <v>1</v>
+      </c>
+      <c r="F2" s="3">
+        <v>2</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I2" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="108">
+      <c r="A3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" s="3">
+        <v>2</v>
+      </c>
+      <c r="E3" s="3">
+        <v>1</v>
+      </c>
+      <c r="F3" s="3">
+        <v>2</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I3" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="67.5">
+      <c r="A4" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="3">
+        <v>2</v>
+      </c>
+      <c r="E4" s="3">
+        <v>1</v>
+      </c>
+      <c r="F4" s="3">
+        <v>2</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H4" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="67.5">
-      <c r="A3" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D3" s="4">
-        <v>2</v>
-      </c>
-      <c r="E3" s="4">
-        <v>1</v>
-      </c>
-      <c r="F3" s="4">
-        <v>2</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="I3" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="108">
-      <c r="A4" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D4" s="4">
-        <v>2</v>
-      </c>
-      <c r="E4" s="4">
-        <v>1</v>
-      </c>
-      <c r="F4" s="4">
-        <v>2</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="I4" s="4">
+      <c r="I4" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="67.5">
       <c r="A5" s="2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D5" s="4">
-        <v>2</v>
-      </c>
-      <c r="E5" s="4">
-        <v>1</v>
-      </c>
-      <c r="F5" s="4">
+        <v>21</v>
+      </c>
+      <c r="D5" s="3">
+        <v>2</v>
+      </c>
+      <c r="E5" s="3">
+        <v>1</v>
+      </c>
+      <c r="F5" s="3">
         <v>2</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="I5" s="4">
+        <v>16</v>
+      </c>
+      <c r="I5" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="67.5">
       <c r="A6" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D6" s="4">
-        <v>2</v>
-      </c>
-      <c r="E6" s="4">
-        <v>1</v>
-      </c>
-      <c r="F6" s="4">
+      <c r="D6" s="3">
+        <v>2</v>
+      </c>
+      <c r="E6" s="3">
+        <v>1</v>
+      </c>
+      <c r="F6" s="3">
         <v>2</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="I6" s="4">
+        <v>18</v>
+      </c>
+      <c r="I6" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="67.5">
       <c r="A7" s="2" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D7" s="4">
-        <v>2</v>
-      </c>
-      <c r="E7" s="4">
-        <v>1</v>
-      </c>
-      <c r="F7" s="4">
+        <v>21</v>
+      </c>
+      <c r="D7" s="3">
+        <v>2</v>
+      </c>
+      <c r="E7" s="3">
+        <v>1</v>
+      </c>
+      <c r="F7" s="3">
         <v>2</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I7" s="4">
+        <v>20</v>
+      </c>
+      <c r="I7" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="67.5">
       <c r="A8" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D8" s="4">
-        <v>2</v>
-      </c>
-      <c r="E8" s="4">
-        <v>1</v>
-      </c>
-      <c r="F8" s="4">
-        <v>2</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="I8" s="4">
-        <v>1</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="B8"/>
+      <c r="C8" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" s="5">
+        <v>2</v>
+      </c>
+      <c r="E8" s="5">
+        <v>1</v>
+      </c>
+      <c r="F8" s="5">
+        <v>1</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I8"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <tableParts count="1">

--- a/internal_doc/05.测试设计/OM/数据操作/OM-数据操作（主界面）-测试用例.xlsx
+++ b/internal_doc/05.测试设计/OM/数据操作/OM-数据操作（主界面）-测试用例.xlsx
@@ -838,7 +838,9 @@
       <c r="H8" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="I8"/>
+      <c r="I8" s="3">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
